--- a/Data Files/normalization metric name.xlsx
+++ b/Data Files/normalization metric name.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Metric Name</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>613`8735`5`@#$%%^&amp;(*&amp;*((*~(^#)~#~_#)~(bhjbjsv364949633@@#%^^^&amp;vvVGHFUVBQD@%^*&amp;(VV DJ*^*^^^(*^&amp;*&amp;*&amp;*4</t>
-  </si>
-  <si>
-    <t>The information nnmade available through this web portal is intended solely for authorized users and12</t>
   </si>
   <si>
     <t>value</t>
@@ -1190,8 +1187,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="108.571428571429" customWidth="1"/>
   </cols>
@@ -1216,11 +1213,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1238,7 +1230,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1">
